--- a/LIBETEE_KOREA_次回支払い算出.xlsx
+++ b/LIBETEE_KOREA_次回支払い算出.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet name="次回支払い算出" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="リベティ_支出状況" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="支出詳細" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="今後の予想費用" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="スーツケース_仕入状況" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="販売価格・利益計算" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="リベティ_支出状況" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="支出詳細" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="今後の予想費用" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="スーツケース_仕入状況" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -244,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -576,6 +577,23 @@
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -778,6 +796,21 @@
     <comment ref="D38" authorId="0" shapeId="0">
       <text>
         <t>参考値。実際のレートに書き換えてください（黄色セルが入力欄）。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>S 21,900／M 27,900 の刻み（+6,000円）と、S 100,000／M 150,000ウォンの刻み（+50,000ウォン）から推定した仮の値です。確定価格・確定原価に置き換えてください。</t>
       </text>
     </comment>
   </commentList>
@@ -1785,6 +1818,682 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="45" min="1" max="1"/>
+    <col width="18" customWidth="1" style="45" min="2" max="2"/>
+    <col width="15" customWidth="1" style="45" min="3" max="3"/>
+    <col width="14" customWidth="1" style="45" min="4" max="4"/>
+    <col width="10" customWidth="1" style="45" min="5" max="5"/>
+    <col width="16" customWidth="1" style="45" min="6" max="6"/>
+    <col width="14" customWidth="1" style="45" min="7" max="7"/>
+    <col width="14" customWidth="1" style="45" min="8" max="8"/>
+    <col width="10" customWidth="1" style="45" min="9" max="9"/>
+    <col width="46" customWidth="1" style="45" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="185" t="inlineStr">
+        <is>
+          <t>LIBETEE KOREA 販売価格・1個あたり利益計算</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="174" t="inlineStr">
+        <is>
+          <t>通貨: 日本円（JPY）／ 原価は韓国ウォン建てを為替レートで換算</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="175" t="inlineStr">
+        <is>
+          <t>① 前提条件（黄色セル＝入力欄）</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
+      <c r="I4" s="1" t="n"/>
+      <c r="J4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>為替レート（1ウォン = ○円）</t>
+        </is>
+      </c>
+      <c r="C5" s="186">
+        <f>'次回支払い算出'!D38</f>
+        <v>0.11</v>
+      </c>
+      <c r="J5" s="174" t="inlineStr">
+        <is>
+          <t>「次回支払い算出」D38と連動。実レートに更新してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>決済・販売手数料率</t>
+        </is>
+      </c>
+      <c r="C6" s="187" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J6" s="174" t="inlineStr">
+        <is>
+          <t>ご指定の4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>送料（円／個）</t>
+        </is>
+      </c>
+      <c r="C7" s="188" t="n">
+        <v>300</v>
+      </c>
+      <c r="J7" s="174" t="inlineStr">
+        <is>
+          <t>ご指定の300円</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="175" t="inlineStr">
+        <is>
+          <t>② サイズ別 1個あたり利益</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="1" t="n"/>
+      <c r="I9" s="1" t="n"/>
+      <c r="J9" s="1" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="189" t="inlineStr">
+        <is>
+          <t>サイズ</t>
+        </is>
+      </c>
+      <c r="B10" s="189" t="inlineStr">
+        <is>
+          <t>販売状態</t>
+        </is>
+      </c>
+      <c r="C10" s="189" t="inlineStr">
+        <is>
+          <t>販売価格(円)</t>
+        </is>
+      </c>
+      <c r="D10" s="189" t="inlineStr">
+        <is>
+          <t>手数料(4%)</t>
+        </is>
+      </c>
+      <c r="E10" s="189" t="inlineStr">
+        <is>
+          <t>送料(円)</t>
+        </is>
+      </c>
+      <c r="F10" s="189" t="inlineStr">
+        <is>
+          <t>原価(ウォン)</t>
+        </is>
+      </c>
+      <c r="G10" s="189" t="inlineStr">
+        <is>
+          <t>原価(円)</t>
+        </is>
+      </c>
+      <c r="H10" s="189" t="inlineStr">
+        <is>
+          <t>粗利(円)</t>
+        </is>
+      </c>
+      <c r="I10" s="189" t="inlineStr">
+        <is>
+          <t>粗利率</t>
+        </is>
+      </c>
+      <c r="J10" s="189" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="141" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>在庫あり（18個）</t>
+        </is>
+      </c>
+      <c r="C11" s="178" t="n">
+        <v>21900</v>
+      </c>
+      <c r="D11" s="2">
+        <f>C11*$C$6</f>
+        <v>876</v>
+      </c>
+      <c r="E11" s="2">
+        <f>$C$7</f>
+        <v>300</v>
+      </c>
+      <c r="F11" s="177">
+        <f>'スーツケース_仕入状況'!C12</f>
+        <v>100000</v>
+      </c>
+      <c r="G11" s="2">
+        <f>F11*$C$5</f>
+        <v>11000</v>
+      </c>
+      <c r="H11" s="190">
+        <f>C11-D11-E11-G11</f>
+        <v>9724</v>
+      </c>
+      <c r="I11" s="28">
+        <f>IFERROR(H11/C11,0)</f>
+        <v>0.44401826484018264</v>
+      </c>
+      <c r="J11" s="191" t="inlineStr">
+        <is>
+          <t>ご指定の販売価格。原価は今回入荷分S単価</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>在庫あり（15個）</t>
+        </is>
+      </c>
+      <c r="C12" s="178" t="n">
+        <v>27900</v>
+      </c>
+      <c r="D12" s="2">
+        <f>C12*$C$6</f>
+        <v>1116</v>
+      </c>
+      <c r="E12" s="2">
+        <f>$C$7</f>
+        <v>300</v>
+      </c>
+      <c r="F12" s="177">
+        <f>'スーツケース_仕入状況'!C13</f>
+        <v>150000</v>
+      </c>
+      <c r="G12" s="2">
+        <f>F12*$C$5</f>
+        <v>16500</v>
+      </c>
+      <c r="H12" s="190">
+        <f>C12-D12-E12-G12</f>
+        <v>9984</v>
+      </c>
+      <c r="I12" s="28">
+        <f>IFERROR(H12/C12,0)</f>
+        <v>0.3578494623655914</v>
+      </c>
+      <c r="J12" s="191" t="inlineStr">
+        <is>
+          <t>ご指定の販売価格。原価は今回入荷分M単価</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="141" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>予約注文（在庫なし・入荷待ち）</t>
+        </is>
+      </c>
+      <c r="C13" s="188" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D13" s="2">
+        <f>C13*$C$6</f>
+        <v>1356</v>
+      </c>
+      <c r="E13" s="2">
+        <f>$C$7</f>
+        <v>300</v>
+      </c>
+      <c r="F13" s="188" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G13" s="2">
+        <f>F13*$C$5</f>
+        <v>22000</v>
+      </c>
+      <c r="H13" s="190">
+        <f>C13-D13-E13-G13</f>
+        <v>10244</v>
+      </c>
+      <c r="I13" s="28">
+        <f>IFERROR(H13/C13,0)</f>
+        <v>0.30218289085545724</v>
+      </c>
+      <c r="J13" s="191" t="inlineStr">
+        <is>
+          <t>★ 販売価格・原価とも未指定のため仮置き。要確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="175" t="inlineStr">
+        <is>
+          <t>③ 今回入荷33個（S18・M15）を完売した場合 ※Lは在庫なしのため除外</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="1" t="n"/>
+      <c r="E15" s="1" t="n"/>
+      <c r="F15" s="1" t="n"/>
+      <c r="G15" s="1" t="n"/>
+      <c r="H15" s="1" t="n"/>
+      <c r="I15" s="1" t="n"/>
+      <c r="J15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="192" t="inlineStr">
+        <is>
+          <t>サイズ</t>
+        </is>
+      </c>
+      <c r="B16" s="192" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C16" s="192" t="inlineStr">
+        <is>
+          <t>1個あたり粗利(円)</t>
+        </is>
+      </c>
+      <c r="D16" s="192" t="inlineStr">
+        <is>
+          <t>粗利合計(円)</t>
+        </is>
+      </c>
+      <c r="J16" s="192" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B17" s="177">
+        <f>'スーツケース_仕入状況'!B12</f>
+        <v>18</v>
+      </c>
+      <c r="C17" s="2">
+        <f>H11</f>
+        <v>9724</v>
+      </c>
+      <c r="D17" s="2">
+        <f>B17*C17</f>
+        <v>175032</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B18" s="177">
+        <f>'スーツケース_仕入状況'!B13</f>
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
+        <f>H12</f>
+        <v>9984</v>
+      </c>
+      <c r="D18" s="2">
+        <f>B18*C18</f>
+        <v>149760</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="121" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B19" s="129">
+        <f>SUM(B17:B18)</f>
+        <v>33</v>
+      </c>
+      <c r="C19" s="120" t="n"/>
+      <c r="D19" s="129">
+        <f>SUM(D17:D18)</f>
+        <v>324792</v>
+      </c>
+      <c r="E19" s="120" t="n"/>
+      <c r="F19" s="120" t="n"/>
+      <c r="G19" s="120" t="n"/>
+      <c r="H19" s="120" t="n"/>
+      <c r="I19" s="120" t="n"/>
+      <c r="J19" s="120" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="175" t="inlineStr">
+        <is>
+          <t>④ 次回支払いとの比較・損益分岐</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="n"/>
+      <c r="D21" s="1" t="n"/>
+      <c r="E21" s="1" t="n"/>
+      <c r="F21" s="1" t="n"/>
+      <c r="G21" s="1" t="n"/>
+      <c r="H21" s="1" t="n"/>
+      <c r="I21" s="1" t="n"/>
+      <c r="J21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>次回支払い 合計見込み（円）</t>
+        </is>
+      </c>
+      <c r="D22" s="2">
+        <f>'次回支払い算出'!D39</f>
+        <v>1373395.0476190476</v>
+      </c>
+      <c r="J22" s="174" t="inlineStr">
+        <is>
+          <t>「次回支払い算出」③×為替レート</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>33個完売時の粗利合計（円）</t>
+        </is>
+      </c>
+      <c r="D23" s="2">
+        <f>D19</f>
+        <v>324792</v>
+      </c>
+      <c r="J23" s="174" t="inlineStr">
+        <is>
+          <t>③より</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="141" t="inlineStr">
+        <is>
+          <t>次回支払いのカバー率</t>
+        </is>
+      </c>
+      <c r="D24" s="193">
+        <f>IFERROR(D23/D22,0)</f>
+        <v>0.23648840190815282</v>
+      </c>
+      <c r="J24" s="174" t="inlineStr">
+        <is>
+          <t>33個では次回支払いを賄えません</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>不足額（円）</t>
+        </is>
+      </c>
+      <c r="D25" s="2">
+        <f>D22-D23</f>
+        <v>1048603.0476190476</v>
+      </c>
+      <c r="J25" s="174" t="inlineStr">
+        <is>
+          <t>追加販売で埋める必要がある金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S:M=18:15 構成の平均粗利（円/個）</t>
+        </is>
+      </c>
+      <c r="D26" s="2">
+        <f>IFERROR(D19/B19,0)</f>
+        <v>9842.181818181818</v>
+      </c>
+      <c r="J26" s="174" t="inlineStr">
+        <is>
+          <t>③の加重平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>損益分岐 必要販売数（S単独）</t>
+        </is>
+      </c>
+      <c r="D27" s="2">
+        <f>ROUNDUP(D22/H11,0)</f>
+        <v>142</v>
+      </c>
+      <c r="J27" s="174" t="inlineStr">
+        <is>
+          <t>次回支払いを粗利で回収するのに必要な個数</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>損益分岐 必要販売数（M単独）</t>
+        </is>
+      </c>
+      <c r="D28" s="2">
+        <f>ROUNDUP(D22/H12,0)</f>
+        <v>138</v>
+      </c>
+      <c r="J28" s="174" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="141" t="inlineStr">
+        <is>
+          <t>損益分岐 必要販売数（18:15構成）</t>
+        </is>
+      </c>
+      <c r="D29" s="129">
+        <f>ROUNDUP(D22/D26,0)</f>
+        <v>140</v>
+      </c>
+      <c r="J29" s="174" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="175" t="inlineStr">
+        <is>
+          <t>注記・前提</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="1" t="n"/>
+      <c r="D32" s="1" t="n"/>
+      <c r="E32" s="1" t="n"/>
+      <c r="F32" s="1" t="n"/>
+      <c r="G32" s="1" t="n"/>
+      <c r="H32" s="1" t="n"/>
+      <c r="I32" s="1" t="n"/>
+      <c r="J32" s="1" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="180" t="inlineStr">
+        <is>
+          <t>1. 販売価格（S 21,900円／M 27,900円）、手数料率4%、送料300円／個はご指定の値です。</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="1" t="n"/>
+      <c r="D33" s="1" t="n"/>
+      <c r="E33" s="1" t="n"/>
+      <c r="F33" s="1" t="n"/>
+      <c r="G33" s="1" t="n"/>
+      <c r="H33" s="1" t="n"/>
+      <c r="I33" s="1" t="n"/>
+      <c r="J33" s="1" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="180" t="inlineStr">
+        <is>
+          <t>2. L は在庫がないため「予約注文（入荷待ち）」として計上。販売価格・原価はご指定がないため仮置きです（黄色セル）。確定値に置き換えてください。</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="1" t="n"/>
+      <c r="D34" s="1" t="n"/>
+      <c r="E34" s="1" t="n"/>
+      <c r="F34" s="1" t="n"/>
+      <c r="G34" s="1" t="n"/>
+      <c r="H34" s="1" t="n"/>
+      <c r="I34" s="1" t="n"/>
+      <c r="J34" s="1" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="180" t="inlineStr">
+        <is>
+          <t>3. 原価は S 100,000ウォン／M 150,000ウォン（「スーツケース_仕入状況」参照）を為替レートで円換算しています。レートは①のC5セル（「次回支払い算出」D38と連動）。</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="1" t="n"/>
+      <c r="D35" s="1" t="n"/>
+      <c r="E35" s="1" t="n"/>
+      <c r="F35" s="1" t="n"/>
+      <c r="G35" s="1" t="n"/>
+      <c r="H35" s="1" t="n"/>
+      <c r="I35" s="1" t="n"/>
+      <c r="J35" s="1" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="180" t="inlineStr">
+        <is>
+          <t>4. 粗利は 販売価格 −手数料 −送料 −原価 のみを引いた商品単位の粗利です。広告費・人件費・家賃などの固定費は含みません（それらは「次回支払い算出」側で計上）。</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="n"/>
+      <c r="D36" s="1" t="n"/>
+      <c r="E36" s="1" t="n"/>
+      <c r="F36" s="1" t="n"/>
+      <c r="G36" s="1" t="n"/>
+      <c r="H36" s="1" t="n"/>
+      <c r="I36" s="1" t="n"/>
+      <c r="J36" s="1" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="180" t="inlineStr">
+        <is>
+          <t>5. 手数料4%は販売価格（税込）に対する率として計算しています。税抜ベースが正の場合はご連絡ください。</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
+      <c r="D37" s="1" t="n"/>
+      <c r="E37" s="1" t="n"/>
+      <c r="F37" s="1" t="n"/>
+      <c r="G37" s="1" t="n"/>
+      <c r="H37" s="1" t="n"/>
+      <c r="I37" s="1" t="n"/>
+      <c r="J37" s="1" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="180" t="inlineStr">
+        <is>
+          <t>6. 緑字＝他シート参照、青字＝入力値、黄色セル＝要確定の入力欄。</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="1" t="n"/>
+      <c r="E38" s="1" t="n"/>
+      <c r="F38" s="1" t="n"/>
+      <c r="G38" s="1" t="n"/>
+      <c r="H38" s="1" t="n"/>
+      <c r="I38" s="1" t="n"/>
+      <c r="J38" s="1" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A33:J33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2124,7 +2833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4366,7 +5075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4769,7 +5478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/LIBETEE_KOREA_次回支払い算出.xlsx
+++ b/LIBETEE_KOREA_次回支払い算出.xlsx
@@ -1072,7 +1072,7 @@
     <row r="2">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>算出日: 2026-09-08 ／ 通貨: 韓国ウォン（KRW）／ 700個の大量入荷分は算出対象外</t>
+          <t>算出日: 2026-09-11 ／ 通貨: 韓国ウォン（KRW）／ 700個の大量入荷分は算出対象外</t>
         </is>
       </c>
     </row>
